--- a/product_upload/packages/26/file.xlsx
+++ b/product_upload/packages/26/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>CHLOROHISTOL TAB 4 MG.</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-7B179B317AF2</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1026,6 +1036,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>MUCUM 15MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-4781575BD054</t>
         </is>
       </c>
@@ -1049,7 +1064,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1220,6 +1235,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>TRIMOL SUSP</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-EECDADE8EFD6</t>
         </is>
       </c>
@@ -1243,7 +1263,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1406,6 +1426,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>TRIMOL SUSP.</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-C4C24A1CA42A</t>
         </is>
       </c>
@@ -1429,7 +1454,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1588,6 +1613,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>UROXIN 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-1B98049F45B9</t>
         </is>
       </c>
@@ -1611,7 +1641,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1770,6 +1800,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>VC CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-C5265061CB74</t>
         </is>
       </c>
@@ -1793,7 +1828,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1952,6 +1987,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>VIT. A +D ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-A1EE7FF558A0</t>
         </is>
       </c>
@@ -1975,7 +2015,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2138,6 +2178,11 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>THIAVIT 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-15AD251650A6</t>
         </is>
       </c>
@@ -2161,7 +2206,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2320,6 +2365,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>SOFLAX SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-4DC7718C1349</t>
         </is>
       </c>
@@ -2343,7 +2393,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2502,6 +2552,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>SUCRAZIDE 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-5BEDDC83477F</t>
         </is>
       </c>
@@ -2525,7 +2580,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2684,6 +2739,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>SUPRAPROCT-S OINT.</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-2F85665B28DA</t>
         </is>
       </c>
@@ -2707,7 +2767,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2866,6 +2926,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>TENSOTIN 100 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-A6F786715EA0</t>
         </is>
       </c>
@@ -2889,7 +2954,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3048,6 +3113,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>TETRACYCLINE SKIN OINT 3%</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-292646945EF6</t>
         </is>
       </c>
@@ -3071,7 +3141,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3234,6 +3304,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>XYLOLIN 0.05%CHILD NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-2E165AFE7B2A</t>
         </is>
       </c>
@@ -3257,7 +3332,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3420,6 +3495,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>XYLOLIN 0.1% ADULT NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-B5A186FF8B1F</t>
         </is>
       </c>
@@ -3443,7 +3523,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3606,6 +3686,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>MOTRINEX 5 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-82C3511AEE80</t>
         </is>
       </c>
@@ -3629,7 +3714,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3796,6 +3881,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>VEGGIE VITAMIN D3 50000 I.U. Soft Gelatin Capsule</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-333A1F355299</t>
         </is>
       </c>
@@ -3819,7 +3909,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3978,6 +4068,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>VEGGIE VITAMIN D3 50000 I.U. Soft Gelatin Capsule</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-D4D2F06D29F9</t>
         </is>
       </c>
@@ -4001,7 +4096,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4164,6 +4259,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>BERESAR 300 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-197929951DB6</t>
         </is>
       </c>
@@ -4187,7 +4287,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4346,6 +4446,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>BERESAR 150 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-086A30C11183</t>
         </is>
       </c>
@@ -4369,7 +4474,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4528,6 +4633,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>XEMADERM 0.1 % Ointment</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-65F69618BE47</t>
         </is>
       </c>
@@ -4551,7 +4661,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4714,6 +4824,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CINFAVAL 80 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-B4C3AB06F94A</t>
         </is>
       </c>
@@ -4737,7 +4852,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4896,6 +5011,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>CINFAVAL 160 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-C4A43FEE296B</t>
         </is>
       </c>
@@ -4919,7 +5039,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5082,6 +5202,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>MOTRINEX 4 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-E9D3CBAAEF60</t>
         </is>
       </c>
@@ -5105,7 +5230,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5268,6 +5393,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>CINFAVAL 320 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-92ACCF9DF960</t>
         </is>
       </c>
@@ -5291,7 +5421,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5446,6 +5576,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>CO-CINFAVAL</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-F5B336A084F0</t>
         </is>
       </c>
@@ -5469,7 +5604,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5628,6 +5763,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>CO-CINFAVAL</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-FE96D4E40A01</t>
         </is>
       </c>
@@ -5651,7 +5791,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5822,6 +5962,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>VEGGIE Vitamin D3 5,000 IU</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-48D1AA7D0168</t>
         </is>
       </c>
@@ -5845,7 +5990,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6004,6 +6149,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>COVAZ</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-B307AD47904C</t>
         </is>
       </c>
@@ -6027,7 +6177,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6186,6 +6336,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>COVAZ</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-877C104AFE0F</t>
         </is>
       </c>
@@ -6209,7 +6364,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6368,6 +6523,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>COVAZ</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-9A6130E9A2C1</t>
         </is>
       </c>
@@ -6391,7 +6551,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6558,6 +6718,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>DIVAD 10000 I.U Capsule</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-56C416B2D0E2</t>
         </is>
       </c>
@@ -6581,7 +6746,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6740,6 +6905,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>DIVAD 50000 I.U Capsule</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-39D3BC8E2744</t>
         </is>
       </c>
@@ -6763,7 +6933,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6926,6 +7096,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CLARIDAR XL 500 mg Tablet</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-E0FBF9E93799</t>
         </is>
       </c>
@@ -6949,7 +7124,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7108,6 +7283,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>ESPERAL 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-D4AFA4C4DABA</t>
         </is>
       </c>
@@ -7131,7 +7311,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7290,6 +7470,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>ESPERAL 100 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-D55423798CB1</t>
         </is>
       </c>
@@ -7313,7 +7498,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7468,6 +7653,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>ESPERAL 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-115651CF5E37</t>
         </is>
       </c>
@@ -7491,7 +7681,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7650,6 +7840,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CO-CINFAVAL</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-572666C0AF91</t>
         </is>
       </c>
@@ -7673,7 +7868,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7828,6 +8023,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>MOTRINEX 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-A877FBA75DBF</t>
         </is>
       </c>
@@ -7851,7 +8051,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8014,6 +8214,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>LEBALIN 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-FFFD6269EFA9</t>
         </is>
       </c>
@@ -8037,7 +8242,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8196,6 +8401,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>FOSIPRIL 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-E1B5AE218A21</t>
         </is>
       </c>
@@ -8219,7 +8429,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8374,6 +8584,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>NEGAFEN 1% cream</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-280FD6A4A104</t>
         </is>
       </c>
@@ -8397,7 +8612,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8560,6 +8775,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>NEGAFEN 250 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-B187D2EE4496</t>
         </is>
       </c>
@@ -8583,7 +8803,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8746,6 +8966,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>LEBALIN 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-DACB4AC29386</t>
         </is>
       </c>
@@ -8769,7 +8994,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8940,6 +9165,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>LOVRAK 200 mg suspension</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-5F67DF8B1628</t>
         </is>
       </c>
@@ -8963,7 +9193,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9126,6 +9356,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>JULMENTIN ES SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-696456A83ED7</t>
         </is>
       </c>
@@ -9149,7 +9384,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9310,6 +9545,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>IRSOTAN 150 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-18B2F8FB8111</t>
         </is>
       </c>
@@ -9333,7 +9573,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9490,6 +9730,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>IRSOTAN 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-FFBB8ED03EEE</t>
         </is>
       </c>
@@ -9513,7 +9758,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9676,6 +9921,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>LIPIGARD 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-1652FFC9AA04</t>
         </is>
       </c>
@@ -9699,7 +9949,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9862,6 +10112,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>LIPIGARD 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-389BAAB2EF74</t>
         </is>
       </c>
@@ -9885,7 +10140,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10048,6 +10303,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>LIPIGARD 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-FFFDB6C8F9AA</t>
         </is>
       </c>
@@ -10071,7 +10331,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10226,6 +10486,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>LEBALIN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-D0443510309F</t>
         </is>
       </c>
@@ -10249,7 +10514,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10408,6 +10673,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>LEBALIN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-4D0425013B16</t>
         </is>
       </c>
@@ -10431,7 +10701,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10602,6 +10872,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>TYRA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-A953217E8B90</t>
         </is>
       </c>
@@ -10625,7 +10900,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10792,6 +11067,11 @@
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>PARAZOLE 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-97B49A3AD5B3</t>
         </is>
       </c>
@@ -10815,7 +11095,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10982,6 +11262,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>PANDERM SKIN OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-676F626C1756</t>
         </is>
       </c>
@@ -11005,7 +11290,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11168,6 +11453,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>POTENCORT 0.005% OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-268E3DCC465B</t>
         </is>
       </c>
@@ -11191,7 +11481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11350,6 +11640,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>POTENCORT 0.05% CREAM</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-EE47F92EA76B</t>
         </is>
       </c>
@@ -11373,7 +11668,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11544,6 +11839,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>PREMOSAN 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-3C127DB6F7F4</t>
         </is>
       </c>
@@ -11567,7 +11867,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11726,6 +12026,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>PREMOSAN ORAL DROPS 4MG-ML</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-9A5C26D974CE</t>
         </is>
       </c>
@@ -11749,7 +12054,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11904,6 +12209,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>PREMOSAN SYRUP 5MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-893432B36357</t>
         </is>
       </c>
@@ -11927,7 +12237,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12098,6 +12408,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>PANDERM CREAM</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-3C12D5A1BE7A</t>
         </is>
       </c>
@@ -12121,7 +12436,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12284,6 +12599,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ORAMAX 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-D522556AC6E8</t>
         </is>
       </c>
@@ -12307,7 +12627,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12466,6 +12786,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>MYOGESIC</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-E37429D74729</t>
         </is>
       </c>
@@ -12489,7 +12814,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12648,6 +12973,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>NASIVIN DROPS 0.025%</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-D63A70C195C6</t>
         </is>
       </c>
@@ -12671,7 +13001,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12834,6 +13164,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>NASIVIN DROPS 0.05%</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-630B04BC0934</t>
         </is>
       </c>
@@ -12857,7 +13192,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13020,6 +13355,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>NEGAZOLE 500MG TAB.</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-CC5508D19C74</t>
         </is>
       </c>
@@ -13043,7 +13383,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13214,6 +13554,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>OMEPREX 20 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-B3941DCD296A</t>
         </is>
       </c>
@@ -13237,7 +13582,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13400,6 +13745,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>OMEPREX 20 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-2F7CAE8228FD</t>
         </is>
       </c>
@@ -13423,7 +13773,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13590,6 +13940,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>NEGAZOLE 250MG TAB.</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-AC6B652FF613</t>
         </is>
       </c>
@@ -13613,7 +13968,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13772,6 +14127,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>MUCUM 30MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-4C73F242FA11</t>
         </is>
       </c>
@@ -13795,7 +14155,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13954,6 +14314,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>PROFINAL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-09BE2FFE0829</t>
         </is>
       </c>
@@ -13977,7 +14342,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14140,6 +14505,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>PROFINAL 5% GEL</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-90EA6ED35BB3</t>
         </is>
       </c>
@@ -14163,7 +14533,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14322,6 +14692,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>ROXAMED</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-0B156507A2CE</t>
         </is>
       </c>
@@ -14345,7 +14720,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14504,6 +14879,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>RUBICALM CREAM</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-069B923C8CAE</t>
         </is>
       </c>
@@ -14527,7 +14907,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14686,6 +15066,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>SALINAL 41.2MG-ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-D2E7496E4C36</t>
         </is>
       </c>
@@ -14709,7 +15094,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14876,6 +15261,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>SALINAL 42MG CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-F7CC38F257CC</t>
         </is>
       </c>
@@ -14899,7 +15289,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15062,6 +15452,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>SALURIN 40 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-B267565C437C</t>
         </is>
       </c>
@@ -15085,7 +15480,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15248,6 +15643,11 @@
       </c>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>SARF 500MG TAB</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-AE0C4EB8F503</t>
         </is>
       </c>
@@ -15271,7 +15671,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15430,6 +15830,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>SARF 750MG TAB.</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-F0CEA94E8728</t>
         </is>
       </c>
@@ -15453,7 +15858,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15616,6 +16021,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>SCOPINAL 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-D47007E21BE9</t>
         </is>
       </c>
@@ -15639,7 +16049,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15806,6 +16216,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>SCOPINAL TAB 10MG</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-9442F85533A0</t>
         </is>
       </c>
@@ -15829,7 +16244,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15988,6 +16403,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>SEDOFAN SYRUP.</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-A2957B832F02</t>
         </is>
       </c>
@@ -16011,7 +16431,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16182,6 +16602,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>SEDOFAN</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-5D16C9C5DA21</t>
         </is>
       </c>
@@ -16205,7 +16630,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16364,6 +16789,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>SALURIN 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-164D264A620B</t>
         </is>
       </c>
@@ -16387,7 +16817,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16546,6 +16976,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>PROFINAL 400 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-87B6648E916F</t>
         </is>
       </c>
@@ -16569,7 +17004,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16728,6 +17163,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>PROFINAL 600 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-BE9F3D407847</t>
         </is>
       </c>
@@ -16751,7 +17191,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16918,6 +17358,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>PROFINAL Pediatric Suspension</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-64D392124794</t>
         </is>
       </c>
@@ -16941,7 +17386,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17104,6 +17549,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>PROFINAL Pediatric Suspension</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-9ED9C53C555E</t>
         </is>
       </c>
@@ -17127,7 +17577,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17298,6 +17748,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>PROFINAL XP 400MG F.C TABLET</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-0C921C92D31C</t>
         </is>
       </c>
@@ -17321,7 +17776,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17484,6 +17939,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>ROTHACIN 100MG SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-F610628C51D6</t>
         </is>
       </c>
@@ -17507,7 +17967,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17670,6 +18130,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>RISEK</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-460E251B185C</t>
         </is>
       </c>
@@ -17693,7 +18158,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17864,6 +18329,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>RISEK 20 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-5FC93E0C9024</t>
         </is>
       </c>
@@ -17887,7 +18357,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18042,6 +18512,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>ARXIA 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-7D6B2BFA2CDF</t>
         </is>
       </c>
@@ -18065,7 +18540,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18236,6 +18711,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>CHLOROHISTOL SYRUP 2 MG - 5 ML</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-4129F31D2E7C</t>
         </is>
       </c>
@@ -18259,7 +18739,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18426,6 +18906,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>AMURETIC 5MG/50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-0577BC2707A7</t>
         </is>
       </c>
@@ -18449,7 +18934,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18616,6 +19101,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>AMYDRAMINE EXPECTORANT SYRUP</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-51B30AD80E2E</t>
         </is>
       </c>
@@ -18639,7 +19129,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18798,6 +19288,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>AMYDRAMINE EXPECTORANT SYRUP SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-C17BC668F09A</t>
         </is>
       </c>
@@ -18821,7 +19316,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18984,6 +19479,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>AMYDRAMINE II SUGAR FREE SYRUP</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-E5E5FE634D12</t>
         </is>
       </c>
@@ -19007,7 +19507,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19177,6 +19677,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>AMYDRAMINE PAEDIATRIC SYRUP</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-532AB721D84E</t>
         </is>
@@ -19193,7 +19698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19239,100 +19744,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19364,7 +19874,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19379,92 +19889,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-12385</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>415.8</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>186</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19496,7 +20011,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19511,92 +20026,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-16200</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>292.14</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>187</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19628,7 +20148,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19643,92 +20163,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-13149</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>320.58</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>188</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19760,7 +20285,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19775,92 +20300,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-49865</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>303.15</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>189</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19892,7 +20422,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19907,92 +20437,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-99845</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>242.27</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>190</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20024,7 +20559,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20039,92 +20574,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-33989</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>223.53</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Medical Bed / Mattress</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>191</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20156,7 +20696,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20171,92 +20711,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-33486</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>495.6</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>192</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20288,7 +20833,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20303,92 +20848,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-38275</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>20.03</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>193</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20420,7 +20970,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20435,92 +20985,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-59262</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>395.57</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>194</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20552,7 +21107,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20567,92 +21122,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-95265</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>38.18</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>195</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20684,7 +21244,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20699,92 +21259,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-68185</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>88.28</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>196</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20801,7 +21366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20907,6 +21472,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20942,7 +21517,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21007,6 +21582,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-FE8DE6CE1C3C</t>
         </is>
@@ -21043,7 +21628,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21108,6 +21693,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-3EB7F6DC6042</t>
         </is>
@@ -21144,7 +21739,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21209,6 +21804,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-C3B5FE407D47</t>
         </is>
@@ -21245,7 +21850,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21310,6 +21915,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-E997A69C26CD</t>
         </is>
@@ -21346,7 +21961,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21411,6 +22026,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-F412C99F69B7</t>
         </is>
@@ -21447,7 +22072,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21512,6 +22137,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-745CE644ECEC</t>
         </is>
@@ -21548,7 +22183,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21613,6 +22248,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-1AF68804F6BA</t>
         </is>
@@ -21649,7 +22294,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21714,6 +22359,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-D201A2299EC3</t>
         </is>
@@ -21750,7 +22405,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21815,6 +22470,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-03AA4C9244FA</t>
         </is>
@@ -21851,7 +22516,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21916,6 +22581,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-113CE3351B25</t>
         </is>
@@ -21952,7 +22627,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22017,6 +22692,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-D3D86E1FD6FD</t>
         </is>
@@ -22053,7 +22738,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22118,6 +22803,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-636D08D68F18</t>
         </is>
@@ -22154,7 +22849,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22219,6 +22914,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-69A12B26DEFF</t>
         </is>
@@ -22255,7 +22960,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22320,6 +23025,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-B75F03D938C1</t>
         </is>
@@ -22356,7 +23071,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22421,6 +23136,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-D24B9F017C9E</t>
         </is>
@@ -22457,7 +23182,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22522,6 +23247,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-4B4C35F1F529</t>
         </is>
@@ -22558,7 +23293,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22623,6 +23358,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-5DDC0FFDCFF3</t>
         </is>
@@ -22659,7 +23404,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22724,6 +23469,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-6F52A46D2CFA</t>
         </is>
@@ -22760,7 +23515,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22825,6 +23580,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-76F17756F5E2</t>
         </is>
@@ -22861,7 +23626,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22926,6 +23691,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-DC03A0E69C54</t>
         </is>

--- a/product_upload/packages/26/file.xlsx
+++ b/product_upload/packages/26/file.xlsx
@@ -885,8 +885,16 @@
           <t>4107737656-102-601868667651</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MUCUM 15MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>MUCUM 15MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1271,8 +1279,16 @@
           <t>9013428800-734-828681555314</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIMOL SUSP.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TRIMOL SUSP. detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1462,8 +1478,16 @@
           <t>5201475742-958-743643111372</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ UROXIN 400MG TAB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>UROXIN 400MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1649,8 +1673,16 @@
           <t>2094848985-825-803647416300</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VC CHEWABLE TAB</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VC CHEWABLE TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1836,8 +1868,16 @@
           <t>1620878696-739-974470372439</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIT. A +D ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VIT. A +D ORAL DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -2023,8 +2063,16 @@
           <t>1646880633-266-058936639564</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ THIAVIT 100MG TAB</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>THIAVIT 100MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2214,8 +2262,16 @@
           <t>0124452620-170-658538098705</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOFLAX SOLUTION</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>SOFLAX SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2401,8 +2457,16 @@
           <t>4254719440-242-610635083816</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SUCRAZIDE 5MG TAB</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>SUCRAZIDE 5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2588,8 +2652,16 @@
           <t>7148076879-991-455681916734</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SUPRAPROCT-S OINT.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>SUPRAPROCT-S OINT. detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2775,8 +2847,16 @@
           <t>9057713785-088-819102882173</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TENSOTIN 100 MG TAB</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TENSOTIN 100 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2962,8 +3042,16 @@
           <t>0844966069-372-832799505514</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TETRACYCLINE SKIN OINT 3%</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TETRACYCLINE SKIN OINT 3% detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3149,8 +3237,16 @@
           <t>1630186027-595-927940228580</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XYLOLIN 0.05%CHILD NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>XYLOLIN 0.05%CHILD NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3340,8 +3436,16 @@
           <t>7565251966-923-959566437654</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XYLOLIN 0.1% ADULT NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>XYLOLIN 0.1% ADULT NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3531,8 +3635,16 @@
           <t>4058450314-745-881202498960</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOTRINEX 5 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>MOTRINEX 5 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3917,8 +4029,16 @@
           <t>8046089071-485-057048883720</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VEGGIE VITAMIN D3 50000 I.U. Soft Gelatin Capsule</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VEGGIE VITAMIN D3 50000 I.U. Soft Gelatin Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4104,8 +4224,16 @@
           <t>8365298547-532-976205393541</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BERESAR 300 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>BERESAR 300 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4295,8 +4423,16 @@
           <t>0949453235-560-478697840319</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BERESAR 150 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BERESAR 150 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4482,8 +4618,16 @@
           <t>8571787889-507-165840258158</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XEMADERM 0.1 % Ointment</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>XEMADERM 0.1 % Ointment detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4669,8 +4813,16 @@
           <t>3619283888-040-174920413767</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CINFAVAL 80 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CINFAVAL 80 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4860,8 +5012,16 @@
           <t>5616339934-765-602264742899</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CINFAVAL 160 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CINFAVAL 160 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5047,8 +5207,16 @@
           <t>2346870106-862-727545265879</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOTRINEX 4 mg Chewable Tablet</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>MOTRINEX 4 mg Chewable Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5238,8 +5406,16 @@
           <t>4014361086-218-821967548992</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CINFAVAL 320 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>CINFAVAL 320 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5429,8 +5605,16 @@
           <t>2359785859-800-983797769076</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-CINFAVAL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>CO-CINFAVAL detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5612,8 +5796,16 @@
           <t>6359424502-588-615239971217</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-CINFAVAL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>CO-CINFAVAL detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5998,8 +6190,16 @@
           <t>2645743162-017-251028348487</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVAZ</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>COVAZ detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6185,8 +6385,16 @@
           <t>5386409127-478-751294050400</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVAZ</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>COVAZ detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6372,8 +6580,16 @@
           <t>8083670343-309-194420064029</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ COVAZ</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>COVAZ detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6754,8 +6970,16 @@
           <t>4041466778-539-959765523108</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIVAD 50000 I.U Capsule</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>DIVAD 50000 I.U Capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -6941,8 +7165,16 @@
           <t>0385790896-286-895456102546</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CLARIDAR XL 500 mg Tablet</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CLARIDAR XL 500 mg Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7132,8 +7364,16 @@
           <t>0047527607-992-274642012672</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESPERAL 25 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ESPERAL 25 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7319,8 +7559,16 @@
           <t>2946633349-313-470041845280</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESPERAL 100 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ESPERAL 100 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7506,8 +7754,16 @@
           <t>1168169938-438-969890517789</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESPERAL 200 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ESPERAL 200 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7689,8 +7945,16 @@
           <t>5158120169-394-306418976420</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-CINFAVAL</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>CO-CINFAVAL detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7876,8 +8140,16 @@
           <t>8498201947-882-509396569851</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOTRINEX 10 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>MOTRINEX 10 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8059,8 +8331,16 @@
           <t>1696589155-265-508641008686</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEBALIN 150 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>LEBALIN 150 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8250,8 +8530,16 @@
           <t>6763905469-470-816876042919</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FOSIPRIL 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>FOSIPRIL 10 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8437,8 +8725,16 @@
           <t>0273498924-961-357275986643</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEGAFEN 1% cream</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NEGAFEN 1% cream detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8620,8 +8916,16 @@
           <t>2617091812-592-483525164824</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEGAFEN 250 mg tablet</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>NEGAFEN 250 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8811,8 +9115,16 @@
           <t>2589859550-198-890797937926</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEBALIN 300 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>LEBALIN 300 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9201,8 +9513,16 @@
           <t>3110612436-278-461449575755</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ JULMENTIN ES SUSPENSION</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>JULMENTIN ES SUSPENSION detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9392,8 +9712,16 @@
           <t>2640866439-163-515118167184</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRSOTAN 150 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>IRSOTAN 150 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -9581,8 +9909,16 @@
           <t>7880864901-004-829502757141</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRSOTAN 300 mg Film Coated Tablet</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>IRSOTAN 300 mg Film Coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -9766,8 +10102,16 @@
           <t>7368399014-675-134223339984</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIPIGARD 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>LIPIGARD 10 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9957,8 +10301,16 @@
           <t>0492366909-458-546967827218</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIPIGARD 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>LIPIGARD 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10148,8 +10500,16 @@
           <t>6971955014-512-011837918273</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIPIGARD 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>LIPIGARD 40 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10339,8 +10699,16 @@
           <t>4857778150-301-378826226813</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEBALIN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>LEBALIN 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10522,8 +10890,16 @@
           <t>1019753545-101-560946026973</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEBALIN 75 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>LEBALIN 75 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11298,8 +11674,16 @@
           <t>7781600770-388-065657296502</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ POTENCORT 0.005% OINTMENT</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>POTENCORT 0.005% OINTMENT detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11489,8 +11873,16 @@
           <t>5262130284-476-652784801941</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ POTENCORT 0.05% CREAM</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>POTENCORT 0.05% CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11875,8 +12267,16 @@
           <t>2077441989-979-502044209690</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREMOSAN ORAL DROPS 4MG-ML</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>PREMOSAN ORAL DROPS 4MG-ML detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12062,8 +12462,16 @@
           <t>7316573811-124-800659688131</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PREMOSAN SYRUP 5MG-5ML</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>PREMOSAN SYRUP 5MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12444,8 +12852,16 @@
           <t>8967784735-037-702425229698</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORAMAX 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ORAMAX 150MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12635,8 +13051,16 @@
           <t>1315127702-092-527736881453</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MYOGESIC</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>MYOGESIC detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12822,8 +13246,16 @@
           <t>1221027437-569-347341028990</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NASIVIN DROPS 0.025%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>NASIVIN DROPS 0.025% detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13009,8 +13441,16 @@
           <t>4939651068-731-154118709948</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NASIVIN DROPS 0.05%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>NASIVIN DROPS 0.05% detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13200,8 +13640,16 @@
           <t>6346888798-709-052003354147</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEGAZOLE 500MG TAB.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>NEGAZOLE 500MG TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13976,8 +14424,16 @@
           <t>4491538435-156-162131907343</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MUCUM 30MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>MUCUM 30MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14163,8 +14619,16 @@
           <t>6790187749-567-095723691857</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROFINAL 200MG TAB</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>PROFINAL 200MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14350,8 +14814,16 @@
           <t>3517224794-481-766123695857</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROFINAL 5% GEL</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>PROFINAL 5% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14541,8 +15013,16 @@
           <t>2346329988-135-005936305405</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROXAMED</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>ROXAMED detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14728,8 +15208,16 @@
           <t>7985065318-265-876320073405</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RUBICALM CREAM</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>RUBICALM CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14915,8 +15403,16 @@
           <t>5359429957-299-099670771660</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALINAL 41.2MG-ML ORAL DROPS</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>SALINAL 41.2MG-ML ORAL DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15297,8 +15793,16 @@
           <t>0667933267-345-589325708557</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALURIN 40 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>SALURIN 40 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15488,8 +15992,16 @@
           <t>1709893732-516-448558993220</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SARF 500MG TAB</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SARF 500MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15679,8 +16191,16 @@
           <t>0822261256-997-613525636877</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SARF 750MG TAB.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SARF 750MG TAB. detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15866,8 +16386,16 @@
           <t>5327776564-094-787208861715</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SCOPINAL 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SCOPINAL 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16252,8 +16780,16 @@
           <t>1292666095-227-818899134531</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SEDOFAN SYRUP.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SEDOFAN SYRUP. detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16638,8 +17174,16 @@
           <t>8486632109-387-814773813020</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALURIN 5MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SALURIN 5MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16825,8 +17369,16 @@
           <t>6898331255-028-239915914417</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROFINAL 400 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>PROFINAL 400 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17012,8 +17564,16 @@
           <t>2423645327-961-771224085098</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROFINAL 600 mg tablet</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>PROFINAL 600 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17394,8 +17954,16 @@
           <t>6534590430-888-807412505618</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROFINAL Pediatric Suspension</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>PROFINAL Pediatric Suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17784,8 +18352,16 @@
           <t>7512357289-612-940112907066</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROTHACIN 100MG SUPPOSITORIES</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>ROTHACIN 100MG SUPPOSITORIES detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17975,8 +18551,16 @@
           <t>2783613010-603-441145429586</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISEK</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>RISEK detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18365,8 +18949,16 @@
           <t>5809205667-485-688675024200</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARXIA 90MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>ARXIA 90MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19137,8 +19729,16 @@
           <t>8081230213-894-266194885394</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMYDRAMINE EXPECTORANT SYRUP SUGAR FREE</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>AMYDRAMINE EXPECTORANT SYRUP SUGAR FREE detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/26/file.xlsx
+++ b/product_upload/packages/26/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20344,7 +20344,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21966,7 +21966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22047,40 +22047,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22160,38 +22165,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>107.89</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-FE8DE6CE1C3C</t>
         </is>
@@ -22271,38 +22281,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>309.2</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-3EB7F6DC6042</t>
         </is>
@@ -22382,38 +22397,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>130.44</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-C3B5FE407D47</t>
         </is>
@@ -22493,38 +22513,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>200.44</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-E997A69C26CD</t>
         </is>
@@ -22604,38 +22629,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>101.51</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-F412C99F69B7</t>
         </is>
@@ -22715,38 +22745,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>458.29</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-745CE644ECEC</t>
         </is>
@@ -22826,38 +22861,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>62.36</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-1AF68804F6BA</t>
         </is>
@@ -22937,38 +22977,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>252.92</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-D201A2299EC3</t>
         </is>
@@ -23048,38 +23093,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>224.11</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-03AA4C9244FA</t>
         </is>
@@ -23159,38 +23209,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>18.91</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-113CE3351B25</t>
         </is>
@@ -23270,38 +23325,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>473.59</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-D3D86E1FD6FD</t>
         </is>
@@ -23381,38 +23441,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>62.26</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-636D08D68F18</t>
         </is>
@@ -23492,38 +23557,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>104.55</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-69A12B26DEFF</t>
         </is>
@@ -23603,38 +23673,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>447.44</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-B75F03D938C1</t>
         </is>
@@ -23714,38 +23789,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>411.07</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-D24B9F017C9E</t>
         </is>
@@ -23825,38 +23905,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>48.74</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-4B4C35F1F529</t>
         </is>
@@ -23936,38 +24021,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>283.25</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-5DDC0FFDCFF3</t>
         </is>
@@ -24047,38 +24137,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>496.43</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-6F52A46D2CFA</t>
         </is>
@@ -24158,38 +24253,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>354.99</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-76F17756F5E2</t>
         </is>
@@ -24269,38 +24369,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>460.58</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-DC03A0E69C54</t>
         </is>
